--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbMonthReportDetailAsset001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbMonthReportDetailAsset001.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>产品名称</t>
   </si>
@@ -101,12 +101,6 @@
   </si>
   <si>
     <t>1.13.7.a投向金融资产投资公司发行的私募资产管理产品</t>
-  </si>
-  <si>
-    <t>信用债债项评级</t>
-  </si>
-  <si>
-    <t>信用债主体评级</t>
   </si>
   <si>
     <t>信用债使用评级</t>
@@ -137,6 +131,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="1">
+    <numFmt numFmtId="180" formatCode="#,##0.000000_ "/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -203,11 +200,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -513,7 +512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="9" style="1" customWidth="1"/>
@@ -533,23 +532,24 @@
     <col min="18" max="18" width="13.08984375" style="1" customWidth="1"/>
     <col min="19" max="19" width="12.1796875" style="1" customWidth="1"/>
     <col min="20" max="20" width="12.6328125" style="1" customWidth="1"/>
-    <col min="21" max="22" width="8.7265625" style="1"/>
-    <col min="23" max="23" width="11.6328125" style="1" customWidth="1"/>
-    <col min="24" max="25" width="13" style="1" customWidth="1"/>
-    <col min="26" max="26" width="12.81640625" style="1" customWidth="1"/>
-    <col min="27" max="28" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13" style="1" customWidth="1"/>
-    <col min="33" max="33" width="16.54296875" style="1" customWidth="1"/>
-    <col min="34" max="35" width="8.7265625" style="1"/>
+    <col min="21" max="22" width="8.7265625" style="5"/>
+    <col min="23" max="23" width="11.6328125" style="5" customWidth="1"/>
+    <col min="24" max="25" width="13" style="5" customWidth="1"/>
+    <col min="26" max="26" width="12.81640625" style="5" customWidth="1"/>
+    <col min="27" max="27" width="20" style="5" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="20" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13" style="1" customWidth="1"/>
+    <col min="31" max="31" width="16.54296875" style="1" customWidth="1"/>
+    <col min="32" max="33" width="8.7265625" style="1"/>
+    <col min="34" max="34" width="12" style="1" customWidth="1"/>
+    <col min="35" max="35" width="12.26953125" style="1" customWidth="1"/>
     <col min="36" max="36" width="12" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.26953125" style="1" customWidth="1"/>
-    <col min="38" max="38" width="12" style="1" customWidth="1"/>
-    <col min="39" max="39" width="10.453125" style="1" customWidth="1"/>
-    <col min="40" max="16384" width="8.7265625" style="1"/>
+    <col min="37" max="37" width="10.453125" style="1" customWidth="1"/>
+    <col min="38" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
@@ -610,25 +610,25 @@
       <c r="T1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="X1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Y1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="Z1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AA1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="AB1" s="3" t="s">
@@ -660,12 +660,6 @@
       </c>
       <c r="AK1" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="AL1" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM1" s="3" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbMonthReportDetailAsset001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbMonthReportDetailAsset001.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8010"/>
   </bookViews>
   <sheets>
-    <sheet name="G06资产端明细台账" sheetId="5" r:id="rId1"/>
+    <sheet name=" G06资产端明细台账（穿透前）" sheetId="5" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbMonthReportDetailAsset001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbMonthReportDetailAsset001.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>产品名称</t>
   </si>
@@ -52,9 +52,6 @@
     <t>资产到期日</t>
   </si>
   <si>
-    <t>最近开放计划结束日/行权日</t>
-  </si>
-  <si>
     <t>主体名称</t>
   </si>
   <si>
@@ -88,9 +85,6 @@
     <t>应计利息</t>
   </si>
   <si>
-    <t>利息调整</t>
-  </si>
-  <si>
     <t>公允价值变动</t>
   </si>
   <si>
@@ -125,6 +119,10 @@
   </si>
   <si>
     <t>投管三级分类</t>
+  </si>
+  <si>
+    <t>行权日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -512,7 +510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AK1"/>
+  <dimension ref="A1:AJ1"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="9" style="1" customWidth="1"/>
@@ -534,22 +532,22 @@
     <col min="20" max="20" width="12.6328125" style="1" customWidth="1"/>
     <col min="21" max="22" width="8.7265625" style="5"/>
     <col min="23" max="23" width="11.6328125" style="5" customWidth="1"/>
-    <col min="24" max="25" width="13" style="5" customWidth="1"/>
-    <col min="26" max="26" width="12.81640625" style="5" customWidth="1"/>
-    <col min="27" max="27" width="20" style="5" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13" style="1" customWidth="1"/>
-    <col min="31" max="31" width="16.54296875" style="1" customWidth="1"/>
-    <col min="32" max="33" width="8.7265625" style="1"/>
-    <col min="34" max="34" width="12" style="1" customWidth="1"/>
-    <col min="35" max="35" width="12.26953125" style="1" customWidth="1"/>
-    <col min="36" max="36" width="12" style="1" customWidth="1"/>
-    <col min="37" max="37" width="10.453125" style="1" customWidth="1"/>
-    <col min="38" max="16384" width="8.7265625" style="1"/>
+    <col min="24" max="24" width="13" style="5" customWidth="1"/>
+    <col min="25" max="25" width="12.81640625" style="5" customWidth="1"/>
+    <col min="26" max="26" width="20" style="5" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="20" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13" style="1" customWidth="1"/>
+    <col min="30" max="30" width="16.54296875" style="1" customWidth="1"/>
+    <col min="31" max="32" width="8.7265625" style="1"/>
+    <col min="33" max="33" width="12" style="1" customWidth="1"/>
+    <col min="34" max="34" width="12.26953125" style="1" customWidth="1"/>
+    <col min="35" max="35" width="12" style="1" customWidth="1"/>
+    <col min="36" max="36" width="10.453125" style="1" customWidth="1"/>
+    <col min="37" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
@@ -584,82 +582,79 @@
         <v>11</v>
       </c>
       <c r="L1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="Z1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="AB1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AA1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AI1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="AJ1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK1" s="3" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbMonthReportDetailAsset001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbMonthReportDetailAsset001.xlsx
@@ -121,7 +121,7 @@
     <t>投管三级分类</t>
   </si>
   <si>
-    <t>行权日</t>
+    <t>最近开放计划结束日/行权日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -521,7 +521,7 @@
     <col min="9" max="9" width="17.26953125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.90625" style="1" customWidth="1"/>
     <col min="11" max="11" width="17.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.90625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="18.54296875" style="1" customWidth="1"/>
     <col min="13" max="13" width="13.453125" style="1" customWidth="1"/>
     <col min="14" max="14" width="15.08984375" style="1" customWidth="1"/>
     <col min="15" max="15" width="8.90625" style="1" customWidth="1"/>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbMonthReportDetailAsset001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbMonthReportDetailAsset001.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="71">
   <si>
     <t>产品名称</t>
   </si>
@@ -122,6 +122,222 @@
   </si>
   <si>
     <t>最近开放计划结束日/行权日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#{keyList.reportType1}</t>
+  </si>
+  <si>
+    <t>#{keyList.reportType2}</t>
+  </si>
+  <si>
+    <t>#{keyList.reportType3}</t>
+  </si>
+  <si>
+    <t>#{keyList.reportType4}</t>
+  </si>
+  <si>
+    <t>#{keyList.prodId}</t>
+  </si>
+  <si>
+    <t>#{keyList.prodName}</t>
+  </si>
+  <si>
+    <t>#{keyList.isFhxgcpStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.assetCode}</t>
+  </si>
+  <si>
+    <t>#{keyList.assetName}</t>
+  </si>
+  <si>
+    <t>#{keyList.vdateStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.mdateStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.openplanStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.subjectName}</t>
+  </si>
+  <si>
+    <t>#{keyList.rivalParty}</t>
+  </si>
+  <si>
+    <t>#{keyList.rate}</t>
+  </si>
+  <si>
+    <t>#{keyList.ccyStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.industry1Str}</t>
+  </si>
+  <si>
+    <t>#{keyList.industry2Str}</t>
+  </si>
+  <si>
+    <t>#{keyList.industry3Str}</t>
+  </si>
+  <si>
+    <t>#{keyList.industry4Str}</t>
+  </si>
+  <si>
+    <t>#{keyList.privatefundFlagStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.privateprdFlagStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.rating}</t>
+  </si>
+  <si>
+    <t>#{keyList.bondtostockFlagStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.typeFinal}</t>
+  </si>
+  <si>
+    <t>#{keyList.isGovernFund1Str}</t>
+  </si>
+  <si>
+    <t>#{keyList.orgAssetType1Str}</t>
+  </si>
+  <si>
+    <t>#{keyList.orgAssetType2Str}</t>
+  </si>
+  <si>
+    <t>#{keyList.orgAssetType3Str}</t>
+  </si>
+  <si>
+    <t>#{keyList.delayPayAmtDv}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.costAmt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Dv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.intincexp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Dv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.floatIngpl</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Dv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.lossAmt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Dv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.assetvalueA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Dv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -132,26 +348,29 @@
   <numFmts count="1">
     <numFmt numFmtId="180" formatCode="#,##0.000000_ "/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -196,15 +415,16 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="180" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -510,7 +730,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AJ2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="9" style="1" customWidth="1"/>
@@ -657,6 +877,116 @@
         <v>34</v>
       </c>
     </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="V2" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="W2" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="X2" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y2" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z2" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ2" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbMonthReportDetailAsset001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbMonthReportDetailAsset001.xlsx
@@ -217,13 +217,14 @@
   </si>
   <si>
     <r>
-      <t>#{keyList.costAmt</t>
+      <t>#{keyList.intincexp</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>Dv</t>
@@ -233,6 +234,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -242,13 +244,14 @@
   </si>
   <si>
     <r>
-      <t>#{keyList.intincexp</t>
+      <t>#{keyList.floatIngpl</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>Dv</t>
@@ -258,6 +261,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -267,13 +271,14 @@
   </si>
   <si>
     <r>
-      <t>#{keyList.floatIngpl</t>
+      <t>#{keyList.lossAmt</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>Dv</t>
@@ -283,6 +288,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -292,13 +298,14 @@
   </si>
   <si>
     <r>
-      <t>#{keyList.lossAmt</t>
+      <t>#{keyList.assetvalueA</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>Dv</t>
@@ -308,6 +315,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -317,13 +325,14 @@
   </si>
   <si>
     <r>
-      <t>#{keyList.assetvalueA</t>
+      <t>#{keyList.costAmt</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>Dv</t>
@@ -333,6 +342,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -353,24 +363,28 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -750,7 +764,8 @@
     <col min="18" max="18" width="13.08984375" style="1" customWidth="1"/>
     <col min="19" max="19" width="12.1796875" style="1" customWidth="1"/>
     <col min="20" max="20" width="12.6328125" style="1" customWidth="1"/>
-    <col min="21" max="22" width="8.7265625" style="5"/>
+    <col min="21" max="21" width="8.7265625" style="5"/>
+    <col min="22" max="22" width="15.26953125" style="5" customWidth="1"/>
     <col min="23" max="23" width="11.6328125" style="5" customWidth="1"/>
     <col min="24" max="24" width="13" style="5" customWidth="1"/>
     <col min="25" max="25" width="12.81640625" style="5" customWidth="1"/>
@@ -942,19 +957,19 @@
         <v>65</v>
       </c>
       <c r="V2" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="W2" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="W2" s="6" t="s">
+      <c r="X2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="X2" s="6" t="s">
+      <c r="Y2" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="Y2" s="6" t="s">
+      <c r="Z2" s="6" t="s">
         <v>69</v>
-      </c>
-      <c r="Z2" s="6" t="s">
-        <v>70</v>
       </c>
       <c r="AA2" s="1" t="s">
         <v>56</v>
